--- a/testdata/教师导入表.xlsx
+++ b/testdata/教师导入表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,22 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>李俊磊</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13800000001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>16474790234</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>七年级(1)班</t>
+          <t>九年级(1)班</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -473,22 +469,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>翟小菊</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13800000002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>19418268902</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>七年级(2)班</t>
+          <t>九年级(2)班</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -500,22 +492,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>陆梅</t>
+          <t>许秀格</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13800000003</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>14902985587</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>七年级(3)班</t>
+          <t>九年级(3)班</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -527,22 +515,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>杨芳</t>
+          <t>张晓燕</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13800000004</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>13054285734</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>八年级(1)班</t>
+          <t>九年级(4)班</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -554,22 +538,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>白华</t>
+          <t>彭瑞敏</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13800000005</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+          <t>15555780717</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>八年级(2)班</t>
+          <t>九年级(5)班</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -581,22 +561,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>江玲</t>
+          <t>王艳玲</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13800000006</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>16512001809</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>八年级(3)班</t>
+          <t>九年级(6)班</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -608,22 +584,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>夏秀英</t>
+          <t>肖敏杰</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13800000007</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>16371828153</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>九年级(1)班</t>
+          <t>九年级(7)班</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -635,22 +607,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>熊勇</t>
+          <t>赵二磊</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13800000008</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>14661575458</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>九年级(2)班</t>
+          <t>九年级(8)班</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -662,22 +630,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>董敏</t>
+          <t>田孝丽</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13800000009</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+          <t>18891131936</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>九年级(3)班</t>
+          <t>九年级(9)班</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -689,81 +653,161 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>彭超</t>
+          <t>彭松伟</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13800000010</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+          <t>13589049558</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>七年级(1)班</t>
+          <t>九年级(10)班</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>谢芳</t>
+          <t>申明月</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13800000011</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+          <t>14595054236</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>七年级(2)班</t>
+          <t>九年级(11)班</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>王晨</t>
+          <t>许贺丽</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13800000012</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+          <t>18205995310</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>七年级(3)班</t>
+          <t>九年级(12)班</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>李玉</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14178061188</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>九年级(13)班</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>王东振</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13623598861</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>九年级(14)班</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>李盼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15007636016</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>九年级(15)班</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>程鹏飞</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13320556068</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>九年级(16)班</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
